--- a/Etapa Construcción - Iteración 1/Pruebas 1° Tanda de CUs a implementar/Casos de prueba - Kairos - NexTech.xlsx
+++ b/Etapa Construcción - Iteración 1/Pruebas 1° Tanda de CUs a implementar/Casos de prueba - Kairos - NexTech.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="206">
   <si>
     <t>Condición</t>
   </si>
@@ -662,6 +662,9 @@
   <si>
     <t>Defecto identificado: el estado del cronómetro persistía entre sesiones.
 Corrección aplicada: ahora el cronómetro se asocia al usuario actual y se detiene al cambiar de sesión.</t>
+  </si>
+  <si>
+    <t>Centurión Valeria</t>
   </si>
   <si>
     <t>CP20_7_V2</t>
@@ -2730,7 +2733,7 @@
         <v>123</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>139</v>
+        <v>197</v>
       </c>
       <c r="N14" s="15" t="s">
         <v>151</v>
@@ -2747,31 +2750,31 @@
         <v>116</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D15" s="15" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L15" s="15" t="s">
         <v>123</v>

--- a/Etapa Construcción - Iteración 1/Pruebas 1° Tanda de CUs a implementar/Casos de prueba - Kairos - NexTech.xlsx
+++ b/Etapa Construcción - Iteración 1/Pruebas 1° Tanda de CUs a implementar/Casos de prueba - Kairos - NexTech.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="CU01- Iniciar Sesión" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="CU09- Crear TareaCU12Estimar ta" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="CU20- Registrar tiempo por cron" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="CU01- Iniciar Sesión" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="CU09- Crear TareaCU12Estimar ta" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="CU20- Registrar tiempo por cron" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -851,6 +851,10 @@
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
